--- a/restaurant_manager_forms/030_drive_thru_meal_order_form--restaurant_manager_forms.xlsx
+++ b/restaurant_manager_forms/030_drive_thru_meal_order_form--restaurant_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -815,8 +815,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'soda'}</t>
+          <t>soda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Soda'}</t>
+          <t>Soda</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'juice'}</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Juice'}</t>
+          <t>Juice</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'coffee'}</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Coffee'}</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'tea'}</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Tea'}</t>
+          <t>Tea</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ketchup'}</t>
+          <t>ketchup</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Ketchup'}</t>
+          <t>Ketchup</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mustard'}</t>
+          <t>mustard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mustard'}</t>
+          <t>Mustard</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hot_sauce'}</t>
+          <t>hot_sauce</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Hot Sauce'}</t>
+          <t>Hot Sauce</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'burger'}</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Burger'}</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fries'}</t>
+          <t>fries</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fries'}</t>
+          <t>Fries</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'salad'}</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Salad'}</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Chicken'}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'combo'}</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Combo'}</t>
+          <t>Combo</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cheese'}</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cheese'}</t>
+          <t>Cheese</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pickles'}</t>
+          <t>pickles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pickles'}</t>
+          <t>Pickles</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'onions'}</t>
+          <t>onions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Onions'}</t>
+          <t>Onions</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tomatoes'}</t>
+          <t>tomatoes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Tomatoes'}</t>
+          <t>Tomatoes</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'mayo'}</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Mayo'}</t>
+          <t>Mayo</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'ketchup'}</t>
+          <t>ketchup</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Ketchup'}</t>
+          <t>Ketchup</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'mustard'}</t>
+          <t>mustard</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Mustard'}</t>
+          <t>Mustard</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'debit_card'}</t>
+          <t>debit_card</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Debit Card'}</t>
+          <t>Debit Card</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
